--- a/data/seed/portfolio/L-2025-7309/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-7309/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J192"/>
+  <dimension ref="A1:J177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,75 +542,75 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>1663000</v>
+        <v>4047000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Nihol Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>228983163</t>
+          <t>266982392</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000313614286001</t>
+          <t>20208000230733241001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5462 01.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №134/26 от 01.07.2026</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>32563000</v>
+        <v>34947000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>6664000</v>
+        <v>1670000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4960</t>
+          <t>Оплата за продукцию по дог. №213/26, НДС 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>39227000</v>
+        <v>36617000</v>
       </c>
     </row>
     <row r="10">
@@ -622,101 +622,101 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>4587000</v>
+        <v>13971000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7747 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №9987 за поставленный товар</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43814000</v>
+        <v>50588000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>3832000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>1377000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Plastik MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>243809838</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000343952608001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shartnoma №61/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №12/26</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>47646000</v>
+        <v>49211000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>1969000</v>
-      </c>
+      <c r="C12" s="2" t="n">
+        <v>11154000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -726,211 +726,211 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1171</t>
+          <t>Оплата за упаковочные материалы, с/ф №7324</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>49615000</v>
+        <v>38057000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>861000</v>
+        <v>21602000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Bunyodkor Meva Eksport XK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>254655114</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000534268225001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7066</t>
+          <t>Оплата за продукцию по договору №16/26, НДС 12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>50476000</v>
+        <v>59659000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>720000</v>
+        <v>5213000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9681 06.07.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №162 от 03.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>51196000</v>
+        <v>64872000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>2180000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>1447000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Nihol Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>266982392</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000230733241001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9828</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №151 ОТ 03.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>49016000</v>
+        <v>66319000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4419000</v>
+        <v>6967000</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Lazzat Agro Servis AJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>392813520</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000266896818001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №219/26</t>
+          <t>Оплата за сырье по дог. №129/26 от 03.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>44597000</v>
+        <v>59352000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>6883000</v>
+        <v>29082000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>238017280</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000294964721001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5705</t>
+          <t>Предоплата за материалы по дог. №251/26</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>37714000</v>
+        <v>30270000</v>
       </c>
     </row>
     <row r="18">
@@ -940,98 +940,103 @@
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>15158000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>8587000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Предоплата за товар по договору №244/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>22556000</v>
+        <v>38857000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>5053000</v>
+        <v>1876000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yangi Hayot Plastik MChJ</t>
+          <t>Oydin Sut MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>385658031</t>
+          <t>398316373</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000489946310001</t>
+          <t>20208000361428649001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №432 07.07.2026, QQS bilan</t>
+          <t>SHARTNOMA №235/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>27609000</v>
+        <v>40733000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n">
-        <v>968000</v>
-      </c>
+      <c r="C20" s="2" t="n">
+        <v>5381000</v>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Farg'ona Yog'och MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>315947700</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000949409282001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1041,131 +1046,126 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Shartnoma №204/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №58/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>28577000</v>
+        <v>35352000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>3339000</v>
+        <v>11137000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>238017280</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000294964721001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №811</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №74/26, QQS bilan</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>25238000</v>
+        <v>24215000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>71237000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>15158000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>341400515</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №14/26, QQS 12%</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>96475000</v>
+        <v>9057000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>2648000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>3267000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Yangi Hayot Plastik MChJ</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>385658031</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000489946310001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Shartnoma №65/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №235/26</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>99123000</v>
+        <v>5790000</v>
       </c>
     </row>
     <row r="24">
@@ -1177,35 +1177,35 @@
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>2144000</v>
+        <v>2801000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7138 09.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №160/26, НДС 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>101267000</v>
+        <v>8591000</v>
       </c>
     </row>
     <row r="25">
@@ -1215,37 +1215,37 @@
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>839000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>1224000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Urganch Qurilish AJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>311384970</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000721269369001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SHARTNOMA №58/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Арендная плата за июль 2026 г. по договору №71/23</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>102106000</v>
+        <v>7367000</v>
       </c>
     </row>
     <row r="26">
@@ -1256,76 +1256,76 @@
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>1224000</v>
+        <v>3686000</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Urganch Logistik AJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>318897067</t>
+          <t>356318470</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000931615046001</t>
+          <t>20208000558446644001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Оплата за товары согласно с/ф №1789</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>100882000</v>
+        <v>3681000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>17801000</v>
-      </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n">
+        <v>3354000</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shahrisabz Sut XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>381340274</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000214079755001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7303</t>
+          <t>Оплата за продукцию по договору №263/26, НДС 12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>83081000</v>
+        <v>7035000</v>
       </c>
     </row>
     <row r="28">
@@ -1335,63 +1335,58 @@
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>4788000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>341400515</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-7309)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>16307000306993350417</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovr uchun to'lov h/f №8196</t>
+          <t>Kredit shartnomasi L-2025-7309 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>87869000</v>
+        <v>-1065000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>2931000</v>
+        <v>3925000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Oydin Sut MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>398316373</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000361428649001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1401,86 +1396,91 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6241</t>
+          <t>Оплата за товар по счет-фактуре №9758 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>90800000</v>
+        <v>2860000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>8100000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>2849000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-7309)</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>16307000306993350417</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-7309 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Yetkazilgan tovar uchun tolov h/f №7476</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>82700000</v>
+        <v>5709000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>35709000</v>
+        <v>8020000</v>
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Farg'ona Yog'och MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>315947700</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000949409282001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №167/26</t>
+          <t>Оплата за транспортные услуги по договору №98/26</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>46991000</v>
+        <v>-2311000</v>
       </c>
     </row>
     <row r="32">
@@ -1490,63 +1490,63 @@
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>3699000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>10305000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yangi Hayot Plastik MChJ</t>
+          <t>Nihol Mato MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>385658031</t>
+          <t>378449397</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000489946310001</t>
+          <t>20208000327943647001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №113/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №3/26</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>50690000</v>
+        <v>-12616000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>1885000</v>
+        <v>2161000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Oydin Sut MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>398316373</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000361428649001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1556,56 +1556,56 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Shartnoma №272/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №67/26 от 14.07.2026</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>52575000</v>
+        <v>-10455000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>1765000</v>
+        <v>2013000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Shartnoma №48/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №7359 от 16.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>54340000</v>
+        <v>-8442000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
@@ -1636,16 +1636,16 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>52273000</v>
+        <v>-10509000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
@@ -1676,117 +1676,117 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>50206000</v>
+        <v>-12576000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>5273000</v>
+        <v>13917000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №123/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №9033 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>55479000</v>
+        <v>1341000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>866000</v>
+        <v>2575000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Toshkent Tikuv XK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>365803194</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000994631030001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2631 от 16.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №8662 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>56345000</v>
+        <v>3916000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>4066000</v>
+        <v>2416000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Nihol Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>266982392</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000230733241001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1796,637 +1796,637 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №70/26, QQS 12%</t>
+          <t>Оплата по с/ф №8429 за поставленный товар</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>60411000</v>
+        <v>6332000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>1255000</v>
+        <v>1789000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №282/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №4122 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>61666000</v>
+        <v>8121000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>5264000</v>
+        <v>1447000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ishonch Plastik MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>380802310</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000116439042001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3647 22.07.2026, QQS bilan</t>
+          <t>SHARTNOMA №34/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>66930000</v>
+        <v>9568000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>1957000</v>
+        <v>2415000</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>Предоплата за материалы по дог. №218/26</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>64973000</v>
+        <v>7153000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>2483000</v>
+        <v>5335000</v>
       </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Jizzax Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>225550532</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000222183430001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №156/26</t>
+          <t>Оплата за транспортные услуги по дог. №18/26</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>62490000</v>
+        <v>1818000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46226</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>759000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>5402000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Urganch Logistik AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>356318470</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000558446644001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5163 23.07.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №203/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>63249000</v>
+        <v>-3584000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46226</v>
+        <v>46224</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>12020000</v>
-      </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n">
+        <v>1772000</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №219/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №173/26 от 21.07.2026</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>51229000</v>
+        <v>-1812000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46227</v>
+        <v>46224</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>7545000</v>
+        <v>13287000</v>
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Urganch Logistik AJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>356318470</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000558446644001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №131/26 от 24.07.2026, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №119/26, QQS bilan</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>43684000</v>
+        <v>-15099000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>7645000</v>
+        <v>6348000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4487</t>
+          <t>Оплата по счет-фактуре №2508 за поставленный товар</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>51329000</v>
+        <v>-8751000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>1263000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>6774000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Bahor Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>228983163</t>
+          <t>388701360</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000313614286001</t>
+          <t>20208000625890324001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №129/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №229/26</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>52592000</v>
+        <v>-15525000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>765000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>20344000</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000721768980001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Оплата по с/ф №5309 за поставленный товар</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>51827000</v>
+        <v>4819000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>2489000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>7820000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
+          <t>Sharq Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>238017280</t>
+          <t>280231021</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000294964721001</t>
+          <t>20208000643904245001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №242/26, QQS bilan</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №95/26, НДС 12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>49338000</v>
+        <v>12639000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>3793000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>4424000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
+          <t>Nihol Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>238017280</t>
+          <t>266982392</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000294964721001</t>
+          <t>20208000230733241001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7179</t>
+          <t>Предоплата за товар по дог. №209/26 от 23.07.2026</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>45545000</v>
+        <v>17063000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>10695000</v>
+        <v>1977000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Omad Moy MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>274546551</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000465342682001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №166/26</t>
+          <t>Уплата налога на добавленную стоимость за июнь</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>34850000</v>
+        <v>15086000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46231</v>
+        <v>46226</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>1294000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>2433000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tong Farm Savdo MChJ</t>
+          <t>Urganch Logistik AJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>237470234</t>
+          <t>356318470</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000936999144001</t>
+          <t>20208000558446644001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №48/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №57/26, QQS bilan</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>36144000</v>
+        <v>12653000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>5701000</v>
+        <v>7731000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>228983163</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000313614286001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8209 от 29.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №117/26, НДС 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>41845000</v>
+        <v>20384000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>3670000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>1849000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Urganch Logistik AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>356318470</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000558446644001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2436,117 +2436,117 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6418 29.07.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №109/26 от 24.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>45515000</v>
+        <v>18535000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46232</v>
+        <v>46230</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>816000</v>
+        <v>4610000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yangi Hayot Plastik MChJ</t>
+          <t>Shahrisabz Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>385658031</t>
+          <t>351298724</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000489946310001</t>
+          <t>20208000343636620001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8516 2907.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №611 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46331000</v>
+        <v>23145000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>1561000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>765000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000039614925001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2356 от 30.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>47892000</v>
+        <v>22380000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>1149000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>1644000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2556,37 +2556,37 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата по сче-фактуре №3954 за поставленный товар</t>
+          <t>Оплата за упаковочные материалы, с/ №1451</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>49041000</v>
+        <v>20736000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>26232000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>3896000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>238017280</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000294964721001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2596,286 +2596,286 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №124/26</t>
+          <t>Оплата по счет-фактуре №236 за поставленный товар</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>22809000</v>
+        <v>24632000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>4266000</v>
+        <v>1727000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №820 31.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №172/26 от 28.07.2026</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>27075000</v>
+        <v>26359000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за товары согласно счет-фактуре №2450</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>26775000</v>
+        <v>24859000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46237</v>
+        <v>46232</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>5582000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>2202000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Bahor Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>228983163</t>
+          <t>388701360</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000313614286001</t>
+          <t>20208000625890324001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6762</t>
+          <t>Оплата за упаковочные материалы, с/ф №7869</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>32357000</v>
+        <v>22657000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>2733000</v>
+        <v>4106000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8415 03.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №137/26 от 31.07.2026</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>35090000</v>
+        <v>26763000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>2715000</v>
+        <v>2916000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>228983163</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000313614286001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Shartnoma №139/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3376 31.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>37805000</v>
+        <v>29679000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>1667000</v>
+        <v>1431000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Shartnoma №84/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №9114 за поставленный товар</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>39472000</v>
+        <v>31110000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n">
-        <v>801000</v>
-      </c>
+      <c r="C66" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>228983163</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000313614286001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6401 03.08.2026, QQS bilan</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>40273000</v>
+        <v>30810000</v>
       </c>
     </row>
     <row r="67">
@@ -2887,35 +2887,35 @@
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>794000</v>
+        <v>4805000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №382</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8110</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>41067000</v>
+        <v>35615000</v>
       </c>
     </row>
     <row r="68">
@@ -2927,141 +2927,141 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>748000</v>
+        <v>4141000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №618</t>
+          <t>Оплата за продукцию по договору №251/26, НДС 12%</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>41815000</v>
+        <v>39756000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>786000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>2823000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Shahrisabz Sut XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>381340274</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000214079755001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №19/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №273/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>41029000</v>
+        <v>42579000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>9576000</v>
+        <v>1541000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9121 05.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №29/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>50605000</v>
+        <v>44120000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n">
-        <v>1562000</v>
-      </c>
+      <c r="C71" s="2" t="n">
+        <v>3807000</v>
+      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3071,56 +3071,56 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Shartnoma №293/26 bo'yicha oldindan o'lov</t>
+          <t>Tovarlar uchun to'lov h/f №6415</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>52167000</v>
+        <v>40313000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>1049000</v>
+        <v>3830000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №95/26</t>
+          <t>Оплата за транспортные услуги по дог. №44/26</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>51118000</v>
+        <v>36483000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
@@ -3146,37 +3146,37 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №2958</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>35495000</v>
+        <v>20860000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>3616000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>25708000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>238017280</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000294964721001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3186,192 +3186,197 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №187/26 от 07.08.2026, НДС 12%</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №164/26 ОТ 05.08.2026</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>31879000</v>
+        <v>46568000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46244</v>
+        <v>46239</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>986000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>2348000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Shahrisabz Sut XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>381340274</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000214079755001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №101/26</t>
+          <t>Оплата по счет-фактуре №2195 за поставленный товар</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>30893000</v>
+        <v>48916000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46244</v>
+        <v>46239</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1262000</v>
+        <v>4613000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
+          <t>Urganch Logistik AJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>318897067</t>
+          <t>356318470</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000931615046001</t>
+          <t>20208000558446644001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №71/25</t>
+          <t>Оплата за сырье по договору №256/26 от 05.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>29631000</v>
+        <v>44303000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>8100000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>3169000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-7309)</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>16307000306993350417</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-7309 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за товар по счет-фактуре №8389 от 07.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>21531000</v>
+        <v>47472000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>3719000</v>
+        <v>9087000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №294 от 12.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6520 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>25250000</v>
+        <v>56559000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>4618000</v>
+        <v>2240000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Oydin Sut MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>398316373</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000361428649001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3381,157 +3386,152 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Shartnoma №203/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №53/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>29868000</v>
+        <v>58799000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>3249000</v>
+        <v>1824000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>228983163</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000313614286001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №168/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №46/26, НДС 12%</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>33117000</v>
+        <v>60623000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46247</v>
+        <v>46244</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>693000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>1262000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Urganch Qurilish AJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>311384970</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000721269369001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5729 13.08.2026, QQS bilan</t>
+          <t>Ijara haqi avgust oyi uchun, shartnoma №71/23</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>33810000</v>
+        <v>59361000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>2685000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>4761000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Nihol Mato MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>378449397</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000327943647001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №41/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №56/26</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>36495000</v>
+        <v>54600000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>4108000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tong Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>237470234</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-7309)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000936999144001</t>
+          <t>16307000306993350417</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3541,557 +3541,557 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №60/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2025-7309 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>40603000</v>
+        <v>46500000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>3556000</v>
+        <v>6214000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №274/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №160/26 от 11.08.2026</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>44159000</v>
+        <v>52714000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>2862000</v>
+        <v>1281000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №265/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №192/26 от 11.08.2026</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>47021000</v>
+        <v>53995000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n">
-        <v>2519000</v>
-      </c>
+      <c r="C86" s="2" t="n">
+        <v>3350000</v>
+      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yangi Hayot Plastik MChJ</t>
+          <t>Nihol Mato MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>385658031</t>
+          <t>378449397</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000489946310001</t>
+          <t>20208000327943647001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №69/26 от 17.08.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №8723</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>49540000</v>
+        <v>50645000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>2155000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>3626000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Plastik MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>243809838</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000343952608001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1855</t>
+          <t>Предоплата за материалы по дог. №168/26</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>51695000</v>
+        <v>47019000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>2130000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>3842000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Предоплата за товар по договору №11/26 от 13.08.2026</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>49565000</v>
+        <v>50861000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>2130000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>2305000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Предоплата за товар по договору №126/26 от 13.08.2026</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>47435000</v>
+        <v>53166000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46252</v>
+        <v>46247</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>691000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>3949000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №279/26, QQS 12%</t>
+          <t>Оплата за сырье по дог. №294/26 от 13.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>48126000</v>
+        <v>49217000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>50830000</v>
+        <v>2130000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>238017280</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000294964721001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1397</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>-2704000</v>
+        <v>47087000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>2147000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>2130000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1782 за поставленный товар</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>-557000</v>
+        <v>44957000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46254</v>
+        <v>46248</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>19476000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>4569000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Nihol Mato MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>378449397</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000327943647001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №2475 за поставленный товар</t>
+          <t>Оплата за товары согласно счет-фактуре №6647</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>18919000</v>
+        <v>40388000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46254</v>
+        <v>46248</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>6384000</v>
+        <v>7276000</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shahrisabz Sut XK</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>381340274</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000214079755001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №297/26</t>
+          <t>Tovarlar uchun to'lov h/f №1571</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>12535000</v>
+        <v>33112000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46255</v>
+        <v>46251</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>45915000</v>
+        <v>6035000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Afrosiyob Sut MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>277376520</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000864331013001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №277/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №202/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>58450000</v>
+        <v>39147000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>2803000</v>
+        <v>2484000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №177/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №1738 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>61253000</v>
+        <v>41631000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>1465000</v>
+        <v>1460000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Lazzat Moy MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>341164640</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000189194474001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4101,117 +4101,117 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7263</t>
+          <t>Оплата за продукцию по договору №252/26, НДС 12%</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>62718000</v>
+        <v>43091000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>1460000</v>
+        <v>1407000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Sharq Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>280231021</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000643904245001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7983</t>
+          <t>Оплата за товар по счет-фактуре №615 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>64178000</v>
+        <v>44498000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>1047000</v>
+        <v>1234000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6415 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №7575 за поставленный товар</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>65225000</v>
+        <v>45732000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>1044000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>14227000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4221,611 +4221,611 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №10/26, QQS 12%</t>
+          <t>Предоплата за материалы по дог. №98/26</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>66269000</v>
+        <v>31505000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>789000</v>
+        <v>17844000</v>
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Navoiy Plastik MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>243809838</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000721768980001</t>
+          <t>20208000343952608001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Предоплата за материалы по договору №199/26</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>65480000</v>
+        <v>13661000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46258</v>
+        <v>46252</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>1557000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>2113000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №27/26</t>
+          <t>Оплата за товар по счет-фактуре №5890 от 18.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>63923000</v>
+        <v>15774000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>2071000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>5085000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oydin Sut MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>398316373</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000361428649001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Оплата за товар по счет-фактуре №3518 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>61852000</v>
+        <v>20859000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>2494000</v>
+        <v>5738000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
+          <t>Bahor Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>238017280</t>
+          <t>388701360</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000294964721001</t>
+          <t>20208000625890324001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №167/26</t>
+          <t>Предоплата за материалы по договору №71/26</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>59358000</v>
+        <v>15121000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>16170000</v>
+        <v>7987000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №76/26, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №6638</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>43188000</v>
+        <v>7134000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46259</v>
+        <v>46254</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>20272000</v>
+        <v>1163000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chust Metall MChJ</t>
+          <t>Afrosiyob Sut MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>304669823</t>
+          <t>277376520</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000222307332001</t>
+          <t>20208000864331013001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7833 от 25.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №97/26 от 20.08.2026</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>63460000</v>
+        <v>8297000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>1290000</v>
+        <v>5046000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gulshan Trans Servis MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>326411646</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000021891944001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №290/26 от 25.08.2026</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №1648 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>64750000</v>
+        <v>13343000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>1016000</v>
+        <v>3101000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1733</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3402 21.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>65766000</v>
+        <v>16444000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n">
-        <v>834000</v>
-      </c>
+      <c r="C109" s="2" t="n">
+        <v>2109000</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>228983163</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000313614286001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5881 25.08.2026, QQS bilan</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>66600000</v>
+        <v>14335000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>11196000</v>
+        <v>3127000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>238017280</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000294964721001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №285/26</t>
+          <t>Оплата за сырье по договору №102/26 от 21.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>55404000</v>
+        <v>11208000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>3415000</v>
+        <v>6845000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №28 26.08.2026, QQS bilan</t>
+          <t>Shartnoma №46/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>58819000</v>
+        <v>18053000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>1983000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>16727000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Urganch Logistik AJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>356318470</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000558446644001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №249/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №237/26</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>60802000</v>
+        <v>1326000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>1572000</v>
+        <v>23858000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Shahrisabz Sut XK</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>381340274</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000214079755001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №207/26, QQS BILAN</t>
+          <t>Оплата за товары согласно счет-фактуре №7605</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>59230000</v>
+        <v>-22532000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>1378000</v>
+        <v>3230000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4318 27.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №164/26 от 25.08.2026</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>60608000</v>
+        <v>-19302000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>842000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>789000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000039614925001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №105</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>61450000</v>
+        <v>-20091000</v>
       </c>
     </row>
     <row r="116">
@@ -4835,37 +4835,37 @@
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>21627000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>1674000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
+          <t>Afrosiyob Sut MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>238017280</t>
+          <t>277376520</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000294964721001</t>
+          <t>20208000864331013001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №173/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №294/26 от 27.08.2026</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>39823000</v>
+        <v>-18417000</v>
       </c>
     </row>
     <row r="117">
@@ -4876,76 +4876,76 @@
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>22124000</v>
+        <v>5343000</v>
       </c>
       <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №252/26, QQS bilan</t>
+          <t>Предоплата за материалы по договору №186/26</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>17699000</v>
+        <v>-23760000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>624000</v>
+        <v>40604000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №589 28.08.2026, QQS bilan</t>
+          <t>Оплата за товар по с/ф №8351 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>18323000</v>
+        <v>16844000</v>
       </c>
     </row>
     <row r="119">
@@ -4957,35 +4957,35 @@
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>3800000</v>
+        <v>4054000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №9276</t>
+          <t>Оплата за продукцию по дог. №8/26, НДС 12%</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>22123000</v>
+        <v>20898000</v>
       </c>
     </row>
     <row r="120">
@@ -4997,35 +4997,35 @@
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>2664000</v>
+        <v>3810000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Oydin Sut MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>228983163</t>
+          <t>398316373</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000313614286001</t>
+          <t>20208000361428649001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Yetkailgan tovar uchun to'lov h/f №6633</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №266/26, НДС 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>24787000</v>
+        <v>24708000</v>
       </c>
     </row>
     <row r="121">
@@ -5037,35 +5037,35 @@
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>1147000</v>
+        <v>3794000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Chust Metall MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>304669823</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000222307332001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7627 31.08.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №4321 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>25934000</v>
+        <v>28502000</v>
       </c>
     </row>
     <row r="122">
@@ -5077,35 +5077,35 @@
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>920000</v>
+        <v>3518000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №241/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №4937 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>26854000</v>
+        <v>32020000</v>
       </c>
     </row>
     <row r="123">
@@ -5115,352 +5115,352 @@
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>2969000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Sharq Un Mahsulotlari AJ</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>280231021</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000643904245001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Оплата за товар по счет-фактуре №3515 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>26554000</v>
+        <v>34989000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>863000</v>
+        <v>1953000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Afrosiyob Sut MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>277376520</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000864331013001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Shartnoma №44/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2626 31.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>27417000</v>
+        <v>36942000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>5755000</v>
+        <v>1444000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6444 02.09.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №8167 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>33172000</v>
+        <v>38386000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>1574000</v>
+        <v>1437000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3708 от 02.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №264/26, НДС 12%</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>34746000</v>
+        <v>39823000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>1933000</v>
+        <v>300000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>359776240</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №1/26, QQS bilan</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>32813000</v>
+        <v>39523000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n">
-        <v>2497000</v>
-      </c>
+      <c r="C128" s="2" t="n">
+        <v>3308000</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Urganch Logistik AJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>228983163</t>
+          <t>356318470</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000313614286001</t>
+          <t>20208000558446644001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3990 за поставленный товар</t>
+          <t>Оплата за сырье по договору №6/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>35310000</v>
+        <v>36215000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46272</v>
+        <v>46266</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>2145000</v>
+        <v>3607000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Oydin Sut MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>398316373</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000361428649001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7427 07.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №13/26, НДС 12%</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>37455000</v>
+        <v>39822000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>1672000</v>
+        <v>3245000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>228983163</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000313614286001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9507 07.09.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №1544 ОТ 04.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>39127000</v>
+        <v>43067000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>1480000</v>
+        <v>2197000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Shartnoma №168/26 bo'yicha oldindan to'lov</t>
+          <t>MAHSULOT UCHUN TO'LOV, HARTNOMA №176/26, QQS 12%</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>40607000</v>
+        <v>45264000</v>
       </c>
     </row>
     <row r="132">
@@ -5470,37 +5470,37 @@
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n">
-        <v>6101000</v>
-      </c>
-      <c r="D132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n">
+        <v>22932000</v>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №272/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №49/26, НДС 12%</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>34506000</v>
+        <v>68196000</v>
       </c>
     </row>
     <row r="133">
@@ -5510,138 +5510,138 @@
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>14582000</v>
-      </c>
-      <c r="D133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n">
+        <v>7373000</v>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №3248</t>
+          <t>Оплата по счет-фактуре №6587 за поставленный товар</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>19924000</v>
+        <v>75569000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>2019000</v>
+        <v>4357000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4777</t>
+          <t>Оплата за товар по счет-фактуре №5326 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>21943000</v>
+        <v>79926000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>1936000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>9583000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Nihol Mato MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>378449397</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000327943647001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Yetkazlgan tovar uchun to'lov h/f №560</t>
+          <t>Оплата за сырье по договору №272/26 от 07.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>23879000</v>
+        <v>70343000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>1178000</v>
+        <v>14582000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Yulduz Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>318897067</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000931615046001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5651,91 +5651,91 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №71/25</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>22701000</v>
+        <v>55761000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>2910000</v>
+        <v>48533000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Shartnoma №49/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №4792 за поставленный товар</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>25611000</v>
+        <v>104294000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>2198000</v>
+        <v>3834000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Navro'z Oziq-ovqat Savdo AJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>297228046</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000923959290001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8971</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1647</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>27809000</v>
+        <v>108128000</v>
       </c>
     </row>
     <row r="139">
@@ -5747,35 +5747,35 @@
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>1934000</v>
+        <v>1429000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Shartnoma №211/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №217/26 от 09.09.2026</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>29743000</v>
+        <v>109557000</v>
       </c>
     </row>
     <row r="140">
@@ -5786,76 +5786,76 @@
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>4989000</v>
+        <v>1178000</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
+          <t>Urganch Qurilish AJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>238017280</t>
+          <t>311384970</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000294964721001</t>
+          <t>20208000721269369001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №256/26</t>
+          <t>Аренда помещения за сентябрь, дог. №71/23</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>24754000</v>
+        <v>108379000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>9814000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>3716000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Yangi Hayot Plastik MChJ</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>385658031</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000489946310001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7057 от 10.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №347</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>34568000</v>
+        <v>104663000</v>
       </c>
     </row>
     <row r="142">
@@ -5867,35 +5867,35 @@
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>3992000</v>
+        <v>8025000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №254/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №120 за поставленный товар</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>38560000</v>
+        <v>112688000</v>
       </c>
     </row>
     <row r="143">
@@ -5905,103 +5905,98 @@
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>3101000</v>
-      </c>
+      <c r="C143" s="2" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>218739312</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-7309)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>16307000306993350417</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6185</t>
+          <t>Kredit shartnomasi L-2025-7309 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>41661000</v>
+        <v>104588000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>1640000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>1133000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №815</t>
+          <t>Оплата по счет-фактуре №9286 за поставленный товар</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>40021000</v>
+        <v>105721000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>2047000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>3353000</v>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Sharq Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>280231021</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000643904245001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6011,417 +6006,422 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №198/26</t>
+          <t>Предоплата за товар по договору №121/26 от 14.09.2026</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>37974000</v>
+        <v>109074000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n">
-        <v>2166000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n">
+        <v>3279000</v>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №3909</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8766 ОТ 14.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>35808000</v>
+        <v>112353000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>8100000</v>
+        <v>1988000</v>
       </c>
       <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-7309)</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>16307000306993350417</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-7309 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Avgust oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>27708000</v>
+        <v>110365000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>3272000</v>
-      </c>
+      <c r="C148" s="2" t="n">
+        <v>1988000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8125 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>30980000</v>
+        <v>108377000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
       <c r="C149" s="2" t="n"/>
       <c r="D149" s="2" t="n">
-        <v>7461000</v>
+        <v>2106000</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3984</t>
+          <t>Оплата за продукцию по дог. №153/26, НДС 12%</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>38441000</v>
+        <v>110483000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>6810000</v>
-      </c>
+      <c r="C150" s="2" t="n">
+        <v>11394000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Navro'z Oziq-ovqat Savdo AJ</t>
+          <t>Nihol Mato MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>297228046</t>
+          <t>378449397</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000923959290001</t>
+          <t>20208000327943647001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1832 14.09.2026, QQS bilan</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №180/26</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>45251000</v>
+        <v>99089000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="n">
-        <v>2818000</v>
+        <v>2124000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №201/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №128/26 от 18.09.2026</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>48069000</v>
+        <v>101213000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="n">
-        <v>2192000</v>
+        <v>9088000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Tong Farm Savdo MChJ</t>
+          <t>Oydin Sut MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>237470234</t>
+          <t>398316373</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000936999144001</t>
+          <t>20208000361428649001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №166/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №264 21.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>50261000</v>
+        <v>110301000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
       <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="n">
-        <v>985000</v>
+        <v>5060000</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Ziyo Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>347023489</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000699914478001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №40/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №161/26 от 21.09.2026</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>51246000</v>
+        <v>115361000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
       <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="n">
-        <v>949000</v>
+        <v>1424000</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6387 14.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №266/26, НДС 12%</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>52195000</v>
+        <v>116785000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>4408000</v>
-      </c>
+      <c r="C155" s="2" t="n">
+        <v>9515000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Plastik MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>243809838</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000343952608001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9299 от 15.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по дог. №101/26 от 21.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>56603000</v>
+        <v>107270000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>1988000</v>
+        <v>1895000</v>
       </c>
       <c r="D156" s="2" t="n"/>
       <c r="E156" t="inlineStr">
@@ -6446,1391 +6446,791 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>QQS avgust 2026 uchun</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>54615000</v>
+        <v>105375000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
-      <c r="C157" s="2" t="n">
-        <v>1988000</v>
-      </c>
-      <c r="D157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>16483000</v>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
+          <t>Оплата за продукцию по договору №170/26, НДС 12%</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>52627000</v>
+        <v>121858000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>2524000</v>
-      </c>
+      <c r="C158" s="2" t="n">
+        <v>11839000</v>
+      </c>
+      <c r="D158" s="2" t="n"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Jizzax Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>225550532</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000222183430001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №98/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №236/26</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>55151000</v>
+        <v>110019000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
-      <c r="C159" s="2" t="n">
-        <v>2532000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>1859000</v>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №5998</t>
+          <t>Mahsulot uchun to'lov, shartn. №36/26, QQS 12%</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>52619000</v>
+        <v>111878000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>4796000</v>
-      </c>
+      <c r="C160" s="2" t="n">
+        <v>1598000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Nihol Mato MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>378449397</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000327943647001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Shartnoma №64/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по договору №197/26</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>57415000</v>
+        <v>110280000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="B161" t="n">
         <v>253</v>
       </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n">
-        <v>5325000</v>
-      </c>
+      <c r="C161" s="2" t="n">
+        <v>5442000</v>
+      </c>
+      <c r="D161" s="2" t="n"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Nihol Mato MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>378449397</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000327943647001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2235 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно с/ф №469</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>62740000</v>
+        <v>104838000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B162" t="n">
         <v>254</v>
       </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>4721000</v>
-      </c>
+      <c r="C162" s="2" t="n">
+        <v>736000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000039614925001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №235 за поставленный товар</t>
+          <t>Elektr energiyasi uchun to'lov sentyabr</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>67461000</v>
+        <v>104102000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B163" t="n">
         <v>255</v>
       </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>2515000</v>
-      </c>
+      <c r="C163" s="2" t="n">
+        <v>39371000</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Navoiy Plastik MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>243809838</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000343952608001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3605</t>
+          <t>Предоплата за материалы по договору №270/26</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>69976000</v>
+        <v>64731000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B164" t="n">
         <v>256</v>
       </c>
       <c r="C164" s="2" t="n"/>
       <c r="D164" s="2" t="n">
-        <v>2401000</v>
+        <v>3353000</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5352 21.09.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №22/26, НДС 12%</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>72377000</v>
+        <v>68084000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B165" t="n">
         <v>257</v>
       </c>
       <c r="C165" s="2" t="n"/>
       <c r="D165" s="2" t="n">
-        <v>4980000</v>
+        <v>1724000</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Samarqand Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>373931238</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000137673886001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №2/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №34/26, НДС 12%</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>77357000</v>
+        <v>69808000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B166" t="n">
         <v>258</v>
       </c>
       <c r="C166" s="2" t="n"/>
       <c r="D166" s="2" t="n">
-        <v>3643000</v>
+        <v>1376000</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Afrosiyob Tur Servis XK</t>
+          <t>Navoiy Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>341400515</t>
+          <t>240051520</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000057937178001</t>
+          <t>20208000793717890001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Shartnoma №53/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №24/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>81000000</v>
+        <v>71184000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B167" t="n">
         <v>259</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>736000</v>
+        <v>1538000</v>
       </c>
       <c r="D167" s="2" t="n"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Urganch Logistik AJ</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>356318470</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000721768980001</t>
+          <t>20208000558446644001</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+          <t>Предоплата за материалы по договору №94/26</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>80264000</v>
+        <v>69646000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B168" t="n">
         <v>260</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>2040000</v>
+        <v>1649000</v>
       </c>
       <c r="D168" s="2" t="n"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>QO'SHILGAN QIYMAT SOLIG'I AVGUST OYI</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №173/26, QQS bilan</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>78224000</v>
+        <v>67997000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B169" t="n">
         <v>261</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>4557000</v>
+        <v>2247000</v>
       </c>
       <c r="D169" s="2" t="n"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Bahor Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>388701360</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000625890324001</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8990</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №297/26 ОТ 28.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>73667000</v>
+        <v>65750000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="B170" t="n">
         <v>262</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>4261000</v>
+        <v>2343000</v>
       </c>
       <c r="D170" s="2" t="n"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Jizzax Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>225550532</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000222183430001</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №469</t>
+          <t>Xom ashyo uchun to'lov, shartn. №87/26, QQS bilan</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>69406000</v>
+        <v>63407000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="B171" t="n">
         <v>263</v>
       </c>
       <c r="C171" s="2" t="n">
-        <v>4946000</v>
+        <v>3343000</v>
       </c>
       <c r="D171" s="2" t="n"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Toshkent Sut MChJ</t>
+          <t>Farg'ona Yog'och MChJ</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>359776240</t>
+          <t>315947700</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>20208000487148040001</t>
+          <t>20208000949409282001</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №197/26</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №9266</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>64460000</v>
+        <v>60064000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="B172" t="n">
         <v>264</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>23107000</v>
+        <v>4279000</v>
       </c>
       <c r="D172" s="2" t="n"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>238017280</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>20208000294964721001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №268/26</t>
+          <t>Оплата за транспортные услуги по договору №283/26</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>41353000</v>
+        <v>55785000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B173" t="n">
         <v>265</v>
       </c>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n">
-        <v>19415000</v>
-      </c>
+      <c r="C173" s="2" t="n">
+        <v>7501000</v>
+      </c>
+      <c r="D173" s="2" t="n"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
+          <t>Navoiy Plastik MChJ</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>218739312</t>
+          <t>243809838</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>20208000801376738001</t>
+          <t>20208000343952608001</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9091 25.09.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №4900</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>60768000</v>
+        <v>48284000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B174" t="n">
         <v>266</v>
       </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n">
-        <v>860000</v>
-      </c>
+      <c r="C174" s="2" t="n">
+        <v>15884000</v>
+      </c>
+      <c r="D174" s="2" t="n"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Tong Farm Savdo MChJ</t>
+          <t>Nurafshon Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>237470234</t>
+          <t>220215902</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>20208000936999144001</t>
+          <t>20208000727586315001</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №9678</t>
+          <t>Оплата за упаковочные материалы, с/ф №3922</t>
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>61628000</v>
+        <v>32400000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B175" t="n">
         <v>267</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>1793000</v>
+        <v>300000</v>
       </c>
       <c r="D175" s="2" t="n"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Shahrisabz Sut XK</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>381340274</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>20208000214079755001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №270/26</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>59835000</v>
+        <v>32100000</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B176" t="n">
-        <v>268</v>
-      </c>
-      <c r="C176" s="2" t="n"/>
-      <c r="D176" s="2" t="n">
-        <v>18769000</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Afrosiyob Tur Servis XK</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>341400515</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20208000057937178001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №74/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="n">
-        <v>78604000</v>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="n">
+        <v>497267000</v>
+      </c>
+      <c r="D176" s="4" t="n">
+        <v>498467000</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B177" t="n">
-        <v>269</v>
-      </c>
-      <c r="C177" s="2" t="n"/>
-      <c r="D177" s="2" t="n">
-        <v>12801000</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Qarshi Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>228983163</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>20208000313614286001</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9522 28.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="n">
-        <v>91405000</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B178" t="n">
-        <v>270</v>
-      </c>
-      <c r="C178" s="2" t="n"/>
-      <c r="D178" s="2" t="n">
-        <v>3203000</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Afrosiyob Tur Servis XK</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>341400515</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>20208000057937178001</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №5/26 от 28.09.2026</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="n">
-        <v>94608000</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B179" t="n">
-        <v>271</v>
-      </c>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n">
-        <v>1437000</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Afrosiyob Tur Servis XK</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>341400515</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>20208000057937178001</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №7811 28.09.2026, QQS BILAN</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="n">
-        <v>96045000</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B180" t="n">
-        <v>272</v>
-      </c>
-      <c r="C180" s="2" t="n"/>
-      <c r="D180" s="2" t="n">
-        <v>1026000</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Navro'z Oziq-ovqat Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>297228046</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>20208000923959290001</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8537</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="n">
-        <v>97071000</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B181" t="n">
-        <v>273</v>
-      </c>
-      <c r="C181" s="2" t="n">
-        <v>2314000</v>
-      </c>
-      <c r="D181" s="2" t="n"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Toshkent Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>359776240</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>20208000487148040001</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №297/26, QQS BILAN</t>
-        </is>
-      </c>
-      <c r="J181" s="2" t="n">
-        <v>94757000</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B182" t="n">
-        <v>274</v>
-      </c>
-      <c r="C182" s="2" t="n">
-        <v>2720000</v>
-      </c>
-      <c r="D182" s="2" t="n"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Toshkent Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>359776240</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>20208000487148040001</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по дог. №87/26 от 28.09.2026, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J182" s="2" t="n">
-        <v>92037000</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B183" t="n">
-        <v>275</v>
-      </c>
-      <c r="C183" s="2" t="n">
-        <v>3223000</v>
-      </c>
-      <c r="D183" s="2" t="n"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Omad Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>274546551</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>20208000465342682001</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №7255</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="n">
-        <v>88814000</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B184" t="n">
-        <v>276</v>
-      </c>
-      <c r="C184" s="2" t="n">
-        <v>4691000</v>
-      </c>
-      <c r="D184" s="2" t="n"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Shahrisabz Sut XK</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>381340274</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>20208000214079755001</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №4900</t>
-        </is>
-      </c>
-      <c r="J184" s="2" t="n">
-        <v>84123000</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B185" t="n">
-        <v>277</v>
-      </c>
-      <c r="C185" s="2" t="n">
-        <v>10351000</v>
-      </c>
-      <c r="D185" s="2" t="n"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>238017280</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>20208000294964721001</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №87/26</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="n">
-        <v>73772000</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B186" t="n">
-        <v>278</v>
-      </c>
-      <c r="C186" s="2" t="n">
-        <v>21075000</v>
-      </c>
-      <c r="D186" s="2" t="n"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>238017280</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>20208000294964721001</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №283/26</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="n">
-        <v>52697000</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B187" t="n">
-        <v>279</v>
-      </c>
-      <c r="C187" s="2" t="n">
-        <v>29133000</v>
-      </c>
-      <c r="D187" s="2" t="n"/>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Shahrisabz Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>238017280</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>20208000294964721001</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №173/26 от 28.09.2026, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="n">
-        <v>23564000</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B188" t="n">
-        <v>280</v>
-      </c>
-      <c r="C188" s="2" t="n"/>
-      <c r="D188" s="2" t="n">
-        <v>7928000</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Afrosiyob Tur Servis XK</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>341400515</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>20208000057937178001</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №59/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="n">
-        <v>31492000</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B189" t="n">
-        <v>281</v>
-      </c>
-      <c r="C189" s="2" t="n"/>
-      <c r="D189" s="2" t="n">
-        <v>908000</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Nurafshon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>218739312</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>20208000801376738001</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5141 29.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J189" s="2" t="n">
-        <v>32400000</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B190" t="n">
-        <v>282</v>
-      </c>
-      <c r="C190" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D190" s="2" t="n"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Sarbon Moliya Bank</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Bank xizmati uchun komissiya</t>
-        </is>
-      </c>
-      <c r="J190" s="2" t="n">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="n">
         <v>32100000</v>
       </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="n">
-        <v>504513000</v>
-      </c>
-      <c r="D191" s="4" t="n">
-        <v>505713000</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="n">
-        <v>32100000</v>
-      </c>
-      <c r="D192" s="4" t="n"/>
+      <c r="D177" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
